--- a/front.xlsx
+++ b/front.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vidallillo.5\Desktop\Cris\Datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vidallillo.5\Desktop\Cris\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B548"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -4744,6 +4744,30 @@
         <v>1231</v>
       </c>
     </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A546" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B546" s="3">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A547" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B547" s="3">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A548" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B548" s="3">
+        <v>511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
